--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Floating Interest Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Floating Interest Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="185">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Floating Interest Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -76,13 +76,10 @@
     <t>IN0020240019</t>
   </si>
   <si>
-    <t>IN0020230085</t>
-  </si>
-  <si>
-    <t>State Government of Maharashtra</t>
-  </si>
-  <si>
-    <t>IN2220150014</t>
+    <t>IN0020240126</t>
+  </si>
+  <si>
+    <t>^</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds</t>
@@ -97,88 +94,109 @@
     <t>CRISIL AAA</t>
   </si>
   <si>
+    <t>NABARD **</t>
+  </si>
+  <si>
+    <t>INE261F08EM1</t>
+  </si>
+  <si>
+    <t>ICRA AAA</t>
+  </si>
+  <si>
+    <t>INE115A07RF8</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd. **</t>
+  </si>
+  <si>
+    <t>INE093I07074</t>
+  </si>
+  <si>
+    <t>CARE AA+</t>
+  </si>
+  <si>
     <t>Muthoot Finance Ltd. **</t>
   </si>
   <si>
+    <t>INE414G07IQ8</t>
+  </si>
+  <si>
+    <t>CRISIL AA+</t>
+  </si>
+  <si>
+    <t>Mankind Pharma Ltd **</t>
+  </si>
+  <si>
+    <t>INE634S07017</t>
+  </si>
+  <si>
     <t>INE414G07JL7</t>
   </si>
   <si>
-    <t>CRISIL AA+</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd. **</t>
-  </si>
-  <si>
-    <t>INE093I07074</t>
-  </si>
-  <si>
-    <t>CARE AA+</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE414G07IQ8</t>
+    <t>Tata Housing Development Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE582L08045</t>
+  </si>
+  <si>
+    <t>CARE AA</t>
+  </si>
+  <si>
+    <t>INE582L08052</t>
+  </si>
+  <si>
+    <t>ICICI Home Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE071G07777</t>
+  </si>
+  <si>
+    <t>INE261F08DV4</t>
+  </si>
+  <si>
+    <t>Motilal Oswal Home Finance Ltd **</t>
+  </si>
+  <si>
+    <t>INE658R07430</t>
+  </si>
+  <si>
+    <t>ICRA AA</t>
+  </si>
+  <si>
+    <t>Narayana Hrudayalaya Ltd. **</t>
+  </si>
+  <si>
+    <t>INE410P08016</t>
+  </si>
+  <si>
+    <t>360 One Prime Ltd. **</t>
+  </si>
+  <si>
+    <t>INE248U07FA1</t>
+  </si>
+  <si>
+    <t>Pipeline Infrastructure Pvt Ltd. **</t>
+  </si>
+  <si>
+    <t>INE01XX07059</t>
+  </si>
+  <si>
+    <t>INE261F08EK5</t>
   </si>
   <si>
     <t>NABARD</t>
   </si>
   <si>
-    <t>INE261F08EM1</t>
-  </si>
-  <si>
-    <t>ICRA AAA</t>
-  </si>
-  <si>
-    <t>Mankind Pharma Ltd **</t>
-  </si>
-  <si>
-    <t>INE634S07017</t>
-  </si>
-  <si>
-    <t>Tata Housing Development Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE582L08045</t>
-  </si>
-  <si>
-    <t>CARE AA</t>
-  </si>
-  <si>
-    <t>INE582L08052</t>
-  </si>
-  <si>
-    <t>ICICI Home Finance Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE071G07777</t>
-  </si>
-  <si>
-    <t>Narayana Hrudayalaya Ltd. **</t>
-  </si>
-  <si>
-    <t>INE410P08016</t>
-  </si>
-  <si>
-    <t>ICRA AA</t>
-  </si>
-  <si>
-    <t>360 One Prime Ltd. **</t>
-  </si>
-  <si>
-    <t>INE248U07FA1</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Home Finance Ltd **</t>
-  </si>
-  <si>
-    <t>INE658R07430</t>
-  </si>
-  <si>
-    <t>Pipeline Infrastructure Pvt Ltd. **</t>
-  </si>
-  <si>
-    <t>INE01XX07059</t>
+    <t>INE261F08EI9</t>
+  </si>
+  <si>
+    <t>Small Industries Development Bank Of India. **</t>
+  </si>
+  <si>
+    <t>INE556F08KM1</t>
+  </si>
+  <si>
+    <t>INE414G07JF9</t>
   </si>
   <si>
     <t>JM Financial Credit Solution Ltd. **</t>
@@ -187,7 +205,7 @@
     <t>INE651J07960</t>
   </si>
   <si>
-    <t>INE414G07JF9</t>
+    <t>INE582L08060</t>
   </si>
   <si>
     <t>Motilal oswal finvest Ltd **</t>
@@ -199,7 +217,19 @@
     <t>CRISIL AA</t>
   </si>
   <si>
-    <t>INE582L08060</t>
+    <t>Rural Electrification Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE020B08FA2</t>
+  </si>
+  <si>
+    <t>INE556F08KL3</t>
+  </si>
+  <si>
+    <t>INE556F08KN9</t>
+  </si>
+  <si>
+    <t>INE020B08FF1</t>
   </si>
   <si>
     <t>Nirma Ltd. **</t>
@@ -208,51 +238,45 @@
     <t>INE091A07208</t>
   </si>
   <si>
+    <t>Altius Telecom Infrastructure Trust. **</t>
+  </si>
+  <si>
+    <t>INE0BWS08019</t>
+  </si>
+  <si>
+    <t>Godrej Industries Ltd. **</t>
+  </si>
+  <si>
+    <t>INE233A08121</t>
+  </si>
+  <si>
+    <t>JM Financial Products Ltd. **</t>
+  </si>
+  <si>
+    <t>INE523H07CB9</t>
+  </si>
+  <si>
+    <t>Aavas Financiers Ltd. **</t>
+  </si>
+  <si>
+    <t>INE216P07258</t>
+  </si>
+  <si>
+    <t>INE071G07819</t>
+  </si>
+  <si>
     <t>Bharti Telecom Ltd. **</t>
   </si>
   <si>
     <t>INE403D08181</t>
   </si>
   <si>
-    <t>Altius Telecom Infrastructure Trust. **</t>
-  </si>
-  <si>
-    <t>INE0BWS08019</t>
-  </si>
-  <si>
-    <t>Aavas Financiers Ltd. **</t>
-  </si>
-  <si>
-    <t>INE216P07258</t>
-  </si>
-  <si>
-    <t>Godrej Industries Ltd. **</t>
-  </si>
-  <si>
-    <t>INE233A08121</t>
-  </si>
-  <si>
     <t>Manappuram Finance Ltd. **</t>
   </si>
   <si>
-    <t>INE522D07CE4</t>
-  </si>
-  <si>
-    <t>JM Financial Products Ltd. **</t>
-  </si>
-  <si>
-    <t>INE523H07CB9</t>
-  </si>
-  <si>
     <t>INE522D07CD6</t>
   </si>
   <si>
-    <t>Small Industries Development Bank Of India.</t>
-  </si>
-  <si>
-    <t>INE556F08KI9</t>
-  </si>
-  <si>
     <t>DME Development Ltd. **</t>
   </si>
   <si>
@@ -268,87 +292,108 @@
     <t>INE0J7Q07082</t>
   </si>
   <si>
+    <t>INE0J7Q07058</t>
+  </si>
+  <si>
+    <t>INE0J7Q07025</t>
+  </si>
+  <si>
+    <t>INE0J7Q07033</t>
+  </si>
+  <si>
     <t>INE0J7Q07066</t>
   </si>
   <si>
-    <t>INE0J7Q07058</t>
-  </si>
-  <si>
     <t>INE0J7Q07041</t>
   </si>
   <si>
-    <t>INE0J7Q07033</t>
-  </si>
-  <si>
-    <t>INE0J7Q07025</t>
-  </si>
-  <si>
     <t>INE0J7Q07090</t>
   </si>
   <si>
+    <t>EMBASSY OFFICE PARKS REIT **</t>
+  </si>
+  <si>
+    <t>INE041007175</t>
+  </si>
+  <si>
+    <t>Sheela Foam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE916U08012</t>
+  </si>
+  <si>
+    <t>FITCH AA</t>
+  </si>
+  <si>
+    <t>INE916U08038</t>
+  </si>
+  <si>
+    <t>INE916U08020</t>
+  </si>
+  <si>
+    <t>Jodhpur Wind Farms Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE03IQ08033</t>
+  </si>
+  <si>
+    <t>CRISIL AA+(CE)</t>
+  </si>
+  <si>
     <t>Torrent Power Ltd. **</t>
   </si>
   <si>
     <t>INE813H07382</t>
   </si>
   <si>
+    <t>INE634S07025</t>
+  </si>
+  <si>
+    <t>INE813H07390</t>
+  </si>
+  <si>
+    <t>INE261F08EO7</t>
+  </si>
+  <si>
+    <t>INE556F08KK5</t>
+  </si>
+  <si>
+    <t>Eris Lifesciences Ltd. **</t>
+  </si>
+  <si>
+    <t>INE406M08029</t>
+  </si>
+  <si>
+    <t>INE261F08EF5</t>
+  </si>
+  <si>
+    <t>INE406M08011</t>
+  </si>
+  <si>
+    <t>INE556F08KH1</t>
+  </si>
+  <si>
+    <t>INE041007167</t>
+  </si>
+  <si>
+    <t>INE261F08CM5</t>
+  </si>
+  <si>
     <t>Tata Capital Housing Finance Ltd. **</t>
   </si>
   <si>
+    <t>INE033L07HF1</t>
+  </si>
+  <si>
+    <t>Bajaj Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE377Y07482</t>
+  </si>
+  <si>
     <t>INE033L07HZ9</t>
   </si>
   <si>
-    <t>Sheela Foam Ltd. **</t>
-  </si>
-  <si>
-    <t>INE916U08012</t>
-  </si>
-  <si>
-    <t>FITCH AA</t>
-  </si>
-  <si>
-    <t>INE916U08038</t>
-  </si>
-  <si>
-    <t>INE916U08046</t>
-  </si>
-  <si>
-    <t>INE916U08020</t>
-  </si>
-  <si>
-    <t>Jodhpur Wind Farms Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE03IQ08033</t>
-  </si>
-  <si>
-    <t>CRISIL AA+(CE)</t>
-  </si>
-  <si>
-    <t>INE813H07390</t>
-  </si>
-  <si>
-    <t>INE634S07025</t>
-  </si>
-  <si>
-    <t>Eris Lifesciences Ltd. **</t>
-  </si>
-  <si>
-    <t>INE406M08029</t>
-  </si>
-  <si>
-    <t>FITCH AA-</t>
-  </si>
-  <si>
-    <t>INE406M08011</t>
-  </si>
-  <si>
-    <t>INE115A07KM9</t>
-  </si>
-  <si>
-    <t>INE033L07HF1</t>
-  </si>
-  <si>
     <t>INE813H07374</t>
   </si>
   <si>
@@ -385,15 +430,15 @@
     <t>India Universal Trust AL2 **</t>
   </si>
   <si>
+    <t>INE1CBK15037</t>
+  </si>
+  <si>
+    <t>INE1CBK15029</t>
+  </si>
+  <si>
     <t>INE1CBK15011</t>
   </si>
   <si>
-    <t>INE1CBK15037</t>
-  </si>
-  <si>
-    <t>INE1CBK15029</t>
-  </si>
-  <si>
     <t>Term Deposits</t>
   </si>
   <si>
@@ -442,43 +487,52 @@
     <t xml:space="preserve">INTEREST RATE SWAPS (At Notional Value) </t>
   </si>
   <si>
-    <t>Unit trust india- MD -24-Mar-2025 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t>Housing Development Finance Corporation- MD -24-Mar-2025 (Pay fixed/receive float)</t>
+    <t> BNP Paribas- MD -15-Mar-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -13-Jun-2025 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> IDFC FIRST Bank Ltd- MD -23-Apr-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -14-Sep-2026 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -31-Jan-2028 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -03-Feb-2028 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -27-Jan-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -28-Apr-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t>GSCCIL- MD -28-Apr-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -07-Apr-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -26-May-2027 (Pay fixed/receive float)</t>
   </si>
   <si>
     <t> Nomura Fixed Income Securities Ltd- MD -31-Jan-2028 (Pay fixed/receive float)</t>
   </si>
   <si>
-    <t>ICICI Bank Ltd- MD -27-Mar-2025 (Pay fixed/receive float)</t>
-  </si>
-  <si>
     <t> DBS Bank India Ltd- MD -09-Oct-2026 (Pay fixed/receive float)</t>
   </si>
   <si>
-    <t> Barclays Bank- MD -27-Jan-2027 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> BNP Paribas- MD -14-Sep-2026 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t>Housing Development Finance Corporation- MD -14-May-2025 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> Standard Chartered Bank- MD -19-May-2025 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> IDFC FIRST Bank Ltd- MD -20-Mar-2025 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> Barclays Bank- MD -31-Jan-2028 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -03-Feb-2028 (Pay fixed/receive float)</t>
-  </si>
-  <si>
-    <t>Unit trust india- MD -22-May-2025 (Pay fixed/receive float)</t>
+    <t> DBS Bank India Ltd- MD -12-Apr-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t>Housing Development Finance Corporation- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t>IBANK- MD -17-Apr-2030 (Pay fixed/receive float)</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
@@ -487,6 +541,9 @@
     <t>** Non Traded / Illiquid Securities.</t>
   </si>
   <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
@@ -496,7 +553,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -511,17 +568,18 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - NIFTY Low Duration Debt Index A-I</t>
+    <t>Benchmark name - CRISIL Low Duration Debt Index</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="177" formatCode="##0.00"/>
     <numFmt numFmtId="178" formatCode="##0.00%"/>
-    <numFmt numFmtId="179" formatCode="##0"/>
+    <numFmt numFmtId="179" formatCode="\^"/>
+    <numFmt numFmtId="180" formatCode="##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -719,7 +777,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -774,7 +832,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -783,6 +841,10 @@
       <protection/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -900,13 +962,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>151</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>161</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -924,7 +986,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="26479500"/>
+          <a:off x="666750" y="29622750"/>
           <a:ext cx="6391275" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -939,13 +1001,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>149</xdr:row>
+      <xdr:row>166</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>159</xdr:row>
+      <xdr:row>176</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -963,7 +1025,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="29337000"/>
+          <a:off x="666750" y="32480250"/>
           <a:ext cx="6391275" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1297,19 +1359,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J148"/>
+  <dimension ref="B1:J165"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="23" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="23" width="95.85714285714286" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="23" width="17.0" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="23" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="23" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="23" width="13.571428571428571" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="23" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="23" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="23" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="23" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="24" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="24" width="95.85714285714286" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="24" width="17.0" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="24" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="24" width="19.714285714285715" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="24" width="13.571428571428571" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="24" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="24" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="24" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="24" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1397,10 +1459,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>697198.78</v>
+        <v>721446.3599999996</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9685554263050001</v>
+        <v>0.9711810027851002</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1434,10 +1496,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>663536.98</v>
+        <v>692464.3799999997</v>
       </c>
       <c r="H7" s="10">
-        <v>0.921792121514</v>
+        <v>0.9321666699675002</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1471,10 +1533,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>295090.14999999997</v>
+        <v>228703.48</v>
       </c>
       <c r="H9" s="10">
-        <v>0.4099421488265</v>
+        <v>0.3078710869753</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1491,22 +1553,22 @@
         <v>16</v>
       </c>
       <c r="D10" s="14">
-        <v>7.930000000000001</v>
+        <v>7.81</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="15">
-        <v>205981480</v>
+        <v>165122060</v>
       </c>
       <c r="G10" s="16">
-        <v>211257.90</v>
+        <v>171469.68</v>
       </c>
       <c r="H10" s="17">
-        <v>0.2934815597288</v>
+        <v>0.2308253322815</v>
       </c>
       <c r="I10" s="16">
-        <v>7.66</v>
+        <v>7.31</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1520,22 +1582,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="14">
-        <v>7.53</v>
+        <v>6.99</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="15">
-        <v>71446560</v>
+        <v>53446560</v>
       </c>
       <c r="G11" s="16">
-        <v>71967.19</v>
+        <v>54556.32</v>
       </c>
       <c r="H11" s="17">
-        <v>0.0999775306414</v>
+        <v>0.073441442779</v>
       </c>
       <c r="I11" s="16">
-        <v>7.47</v>
+        <v>6.80</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1555,16 +1617,16 @@
         <v>17</v>
       </c>
       <c r="F12" s="15">
-        <v>10009570</v>
+        <v>2509570</v>
       </c>
       <c r="G12" s="16">
-        <v>10250.44</v>
+        <v>2645.54</v>
       </c>
       <c r="H12" s="17">
-        <v>0.0142400124166</v>
+        <v>0.0035613156189</v>
       </c>
       <c r="I12" s="16">
-        <v>6.86</v>
+        <v>6.39</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1578,22 +1640,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>7.18</v>
+        <v>6.79</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="15">
-        <v>1082830</v>
+        <v>30830</v>
       </c>
       <c r="G13" s="16">
-        <v>1112.44</v>
-      </c>
-      <c r="H13" s="17">
-        <v>0.0015454126274</v>
+        <v>31.94</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="I13" s="16">
-        <v>6.87</v>
+        <v>6.37</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1601,35 +1663,35 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="15" customHeight="1">
+      <c r="B15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="14">
-        <v>8.25</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="15">
-        <v>500000</v>
-      </c>
-      <c r="G14" s="16">
-        <v>502.18</v>
-      </c>
-      <c r="H14" s="17">
-        <v>0.0006976334123</v>
-      </c>
-      <c r="I14" s="16">
-        <v>6.72</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" ht="15" customHeight="1">
-      <c r="B15" s="12" t="s">
+      <c r="C15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="9">
+        <v>463760.9000000001</v>
+      </c>
+      <c r="H15" s="10">
+        <v>0.6242955829922</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="11" t="s">
@@ -1637,29 +1699,29 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="9">
-        <v>368446.82999999996</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0.5118499726875</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>13</v>
+      <c r="C16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="14">
+        <v>7.80</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="15">
+        <v>3650</v>
+      </c>
+      <c r="G16" s="16">
+        <v>37266.24</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0.0501662581447</v>
+      </c>
+      <c r="I16" s="16">
+        <v>6.85</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1667,28 +1729,28 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D17" s="14">
-        <v>7.80</v>
+        <v>7.53</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F17" s="15">
-        <v>3650</v>
+        <v>33000</v>
       </c>
       <c r="G17" s="16">
-        <v>36580.96</v>
+        <v>33744.22</v>
       </c>
       <c r="H17" s="17">
-        <v>0.0508186306745</v>
+        <v>0.0454250617023</v>
       </c>
       <c r="I17" s="16">
-        <v>7.70</v>
+        <v>6.61</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -1696,28 +1758,28 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="14">
-        <v>8.65</v>
+        <v>7.58</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F18" s="15">
         <v>20000</v>
       </c>
       <c r="G18" s="16">
-        <v>19987.1</v>
+        <v>20500.02</v>
       </c>
       <c r="H18" s="17">
-        <v>0.0277662765863</v>
+        <v>0.0275962719955</v>
       </c>
       <c r="I18" s="16">
-        <v>8.68</v>
+        <v>7.21</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -1740,13 +1802,13 @@
         <v>20000</v>
       </c>
       <c r="G19" s="16">
-        <v>19943.70</v>
+        <v>20264.36</v>
       </c>
       <c r="H19" s="17">
-        <v>0.027705984878</v>
+        <v>0.0272790363315</v>
       </c>
       <c r="I19" s="16">
-        <v>8.38</v>
+        <v>7.56</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -1763,19 +1825,19 @@
         <v>8.85</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F20" s="15">
         <v>19000</v>
       </c>
       <c r="G20" s="16">
-        <v>19059.70</v>
+        <v>19198.44</v>
       </c>
       <c r="H20" s="17">
-        <v>0.0264779233532</v>
+        <v>0.0258441392804</v>
       </c>
       <c r="I20" s="16">
-        <v>8.63</v>
+        <v>8.03</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -1783,28 +1845,28 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="14">
+        <v>7.99</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="14">
-        <v>7.53</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>37</v>
-      </c>
       <c r="F21" s="15">
-        <v>18000</v>
+        <v>15500</v>
       </c>
       <c r="G21" s="16">
-        <v>18021.40</v>
+        <v>15630.03</v>
       </c>
       <c r="H21" s="17">
-        <v>0.0250355067455</v>
+        <v>0.0210404945546</v>
       </c>
       <c r="I21" s="16">
-        <v>7.50</v>
+        <v>7.09</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -1812,28 +1874,28 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>39</v>
-      </c>
       <c r="D22" s="14">
-        <v>7.99</v>
+        <v>8.65</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F22" s="15">
-        <v>15500</v>
+        <v>15000</v>
       </c>
       <c r="G22" s="16">
-        <v>15513.86</v>
+        <v>15179.99</v>
       </c>
       <c r="H22" s="17">
-        <v>0.0215520074289</v>
+        <v>0.0204346694749</v>
       </c>
       <c r="I22" s="16">
-        <v>8.05</v>
+        <v>8.10</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -1841,28 +1903,28 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="D23" s="14">
         <v>8.27</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" s="15">
         <v>15000</v>
       </c>
       <c r="G23" s="16">
-        <v>15002.36</v>
+        <v>15071.01</v>
       </c>
       <c r="H23" s="17">
-        <v>0.0208414265805</v>
+        <v>0.0202879651438</v>
       </c>
       <c r="I23" s="16">
-        <v>8.16</v>
+        <v>7.08</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -1870,28 +1932,28 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="14">
         <v>8.217500000000001</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F24" s="15">
         <v>12500</v>
       </c>
       <c r="G24" s="16">
-        <v>12497.26</v>
+        <v>12557.63</v>
       </c>
       <c r="H24" s="17">
-        <v>0.017361316936</v>
+        <v>0.0169045578053</v>
       </c>
       <c r="I24" s="16">
-        <v>8.16</v>
+        <v>7.08</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>13</v>
@@ -1899,28 +1961,28 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="D25" s="14">
-        <v>8.14</v>
+        <v>7.48</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F25" s="15">
         <v>12500</v>
       </c>
       <c r="G25" s="16">
-        <v>12485.30</v>
+        <v>12400.95</v>
       </c>
       <c r="H25" s="17">
-        <v>0.0173447019859</v>
+        <v>0.0166936417234</v>
       </c>
       <c r="I25" s="16">
-        <v>8.42</v>
+        <v>7.82</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>13</v>
@@ -1928,28 +1990,28 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D26" s="14">
-        <v>8.25</v>
+        <v>7.62</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F26" s="15">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="G26" s="16">
-        <v>10027.53</v>
+        <v>12280.01</v>
       </c>
       <c r="H26" s="17">
-        <v>0.0139303436445</v>
+        <v>0.0165308373391</v>
       </c>
       <c r="I26" s="16">
-        <v>8.09</v>
+        <v>6.61</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
@@ -1957,13 +2019,13 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D27" s="14">
-        <v>9.3</v>
+        <v>8.55</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>48</v>
@@ -1972,13 +2034,13 @@
         <v>10000</v>
       </c>
       <c r="G27" s="16">
-        <v>9998.61</v>
+        <v>10110.99</v>
       </c>
       <c r="H27" s="17">
-        <v>0.0138901676951</v>
+        <v>0.0136109930714</v>
       </c>
       <c r="I27" s="16">
-        <v>9.29</v>
+        <v>7.74</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
@@ -1986,13 +2048,13 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D28" s="14">
-        <v>8.55</v>
+        <v>8.25</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>48</v>
@@ -2001,13 +2063,13 @@
         <v>10000</v>
       </c>
       <c r="G28" s="16">
-        <v>9991.79</v>
+        <v>10108.26</v>
       </c>
       <c r="H28" s="17">
-        <v>0.0138806932838</v>
+        <v>0.0136073180593</v>
       </c>
       <c r="I28" s="16">
-        <v>8.59</v>
+        <v>7.55</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>13</v>
@@ -2015,28 +2077,28 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D29" s="14">
-        <v>7.96</v>
+        <v>9.3</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="F29" s="15">
-        <v>8800</v>
+        <v>10000</v>
       </c>
       <c r="G29" s="16">
-        <v>8848.41</v>
+        <v>10041.86</v>
       </c>
       <c r="H29" s="17">
-        <v>0.012292298503</v>
+        <v>0.0135179331484</v>
       </c>
       <c r="I29" s="16">
-        <v>7.87</v>
+        <v>8.50</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>13</v>
@@ -2044,28 +2106,28 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D30" s="14">
-        <v>9.3</v>
+        <v>7.96</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F30" s="15">
-        <v>7500</v>
+        <v>8800</v>
       </c>
       <c r="G30" s="16">
-        <v>7561.49</v>
+        <v>8966.16</v>
       </c>
       <c r="H30" s="17">
-        <v>0.0105044965375</v>
+        <v>0.0120698706692</v>
       </c>
       <c r="I30" s="16">
-        <v>9.15</v>
+        <v>6.84</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>13</v>
@@ -2073,28 +2135,28 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D31" s="14">
-        <v>9.02</v>
+        <v>7.44</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F31" s="15">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="G31" s="16">
-        <v>7550.38</v>
+        <v>8667.43</v>
       </c>
       <c r="H31" s="17">
-        <v>0.0104890624158</v>
+        <v>0.0116677328013</v>
       </c>
       <c r="I31" s="16">
-        <v>8.66</v>
+        <v>6.61</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>13</v>
@@ -2102,28 +2164,28 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D32" s="14">
-        <v>9.50</v>
+        <v>7.70</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F32" s="15">
         <v>7500</v>
       </c>
       <c r="G32" s="16">
-        <v>7510.43</v>
+        <v>7670.76</v>
       </c>
       <c r="H32" s="17">
-        <v>0.0104335634815</v>
+        <v>0.0103260572122</v>
       </c>
       <c r="I32" s="16">
-        <v>8.93</v>
+        <v>6.59</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>13</v>
@@ -2131,28 +2193,28 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D33" s="14">
-        <v>8.05</v>
+        <v>7.79</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F33" s="15">
         <v>7500</v>
       </c>
       <c r="G33" s="16">
-        <v>7489.58</v>
+        <v>7662.02</v>
       </c>
       <c r="H33" s="17">
-        <v>0.0104045984557</v>
+        <v>0.0103142917887</v>
       </c>
       <c r="I33" s="16">
-        <v>8.16</v>
+        <v>6.57</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>13</v>
@@ -2160,25 +2222,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D34" s="14">
-        <v>8.50</v>
+        <v>9.02</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F34" s="15">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="G34" s="16">
-        <v>5041.19</v>
+        <v>7636.08</v>
       </c>
       <c r="H34" s="17">
-        <v>0.0070032709029</v>
+        <v>0.0102793724425</v>
       </c>
       <c r="I34" s="16">
         <v>8.04</v>
@@ -2189,28 +2251,28 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D35" s="14">
-        <v>8.90</v>
+        <v>9.3</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F35" s="15">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="G35" s="16">
-        <v>5015.25</v>
+        <v>7601.19</v>
       </c>
       <c r="H35" s="17">
-        <v>0.0069672347989</v>
+        <v>0.0102324049796</v>
       </c>
       <c r="I35" s="16">
-        <v>8.39</v>
+        <v>8.58</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>13</v>
@@ -2218,28 +2280,28 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D36" s="14">
-        <v>8.40</v>
+        <v>8.05</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F36" s="15">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="G36" s="16">
-        <v>5010.4</v>
+        <v>7528.17</v>
       </c>
       <c r="H36" s="17">
-        <v>0.006960497131</v>
+        <v>0.0101341085008</v>
       </c>
       <c r="I36" s="16">
-        <v>8.50</v>
+        <v>7.08</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>13</v>
@@ -2247,28 +2309,28 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D37" s="14">
-        <v>8.42</v>
+        <v>9.50</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F37" s="15">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="G37" s="16">
-        <v>5010.32</v>
+        <v>7527.08</v>
       </c>
       <c r="H37" s="17">
-        <v>0.0069603859942</v>
+        <v>0.0101326411882</v>
       </c>
       <c r="I37" s="16">
-        <v>8.29</v>
+        <v>7.67</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>13</v>
@@ -2276,28 +2338,28 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D38" s="14">
-        <v>8.36</v>
+        <v>7.59</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F38" s="15">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="G38" s="16">
-        <v>5009.52</v>
+        <v>5606.94</v>
       </c>
       <c r="H38" s="17">
-        <v>0.0069592746263</v>
+        <v>0.0075478287973</v>
       </c>
       <c r="I38" s="16">
-        <v>8.17</v>
+        <v>6.52</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>13</v>
@@ -2305,28 +2367,28 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D39" s="14">
-        <v>8.65</v>
+        <v>7.83</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F39" s="15">
         <v>5000</v>
       </c>
       <c r="G39" s="16">
-        <v>4998.39</v>
+        <v>5183.71</v>
       </c>
       <c r="H39" s="17">
-        <v>0.0069438127205</v>
+        <v>0.0069780942216</v>
       </c>
       <c r="I39" s="16">
-        <v>8.63</v>
+        <v>6.59</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>13</v>
@@ -2334,28 +2396,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D40" s="14">
-        <v>8.92</v>
+        <v>7.75</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F40" s="15">
         <v>5000</v>
       </c>
       <c r="G40" s="16">
-        <v>4991.79</v>
+        <v>5108.36</v>
       </c>
       <c r="H40" s="17">
-        <v>0.0069346439353</v>
+        <v>0.006876661194</v>
       </c>
       <c r="I40" s="16">
-        <v>9.35</v>
+        <v>6.57</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>13</v>
@@ -2363,28 +2425,28 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D41" s="14">
-        <v>8.8</v>
+        <v>7.56</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F41" s="15">
         <v>5000</v>
       </c>
       <c r="G41" s="16">
-        <v>4990.31</v>
+        <v>5102.35</v>
       </c>
       <c r="H41" s="17">
-        <v>0.0069325879047</v>
+        <v>0.0068685707826</v>
       </c>
       <c r="I41" s="16">
-        <v>8.86</v>
+        <v>6.53</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
@@ -2392,28 +2454,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D42" s="14">
-        <v>7.44</v>
+        <v>8.50</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F42" s="15">
         <v>5000</v>
       </c>
       <c r="G42" s="16">
-        <v>4984.42</v>
+        <v>5083.32</v>
       </c>
       <c r="H42" s="17">
-        <v>0.0069244054586</v>
+        <v>0.0068429533903</v>
       </c>
       <c r="I42" s="16">
-        <v>7.61</v>
+        <v>7.40</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -2421,28 +2483,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D43" s="14">
-        <v>9.54</v>
+        <v>8.40</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F43" s="15">
-        <v>435</v>
+        <v>5000</v>
       </c>
       <c r="G43" s="16">
-        <v>4621.74</v>
+        <v>5059.87</v>
       </c>
       <c r="H43" s="17">
-        <v>0.0064205668231</v>
+        <v>0.0068113859782</v>
       </c>
       <c r="I43" s="16">
-        <v>9.43</v>
+        <v>7.40</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2450,28 +2512,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D44" s="14">
-        <v>9.54</v>
+        <v>8.36</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F44" s="15">
-        <v>420</v>
+        <v>5000</v>
       </c>
       <c r="G44" s="16">
-        <v>4467.35</v>
+        <v>5059.27</v>
       </c>
       <c r="H44" s="17">
-        <v>0.0062060867113</v>
+        <v>0.0068105782832</v>
       </c>
       <c r="I44" s="16">
-        <v>9.47</v>
+        <v>7.28</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
@@ -2479,28 +2541,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="D45" s="14">
-        <v>9.54</v>
+        <v>8.92</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F45" s="15">
-        <v>420</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="16">
-        <v>4435.50</v>
+        <v>5039.74</v>
       </c>
       <c r="H45" s="17">
-        <v>0.0061618403769</v>
+        <v>0.0067842878117</v>
       </c>
       <c r="I45" s="16">
-        <v>9.28</v>
+        <v>8.48</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2508,28 +2570,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D46" s="14">
-        <v>9.54</v>
+        <v>8.42</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F46" s="15">
-        <v>420</v>
+        <v>5000</v>
       </c>
       <c r="G46" s="16">
-        <v>4430.74</v>
+        <v>5038</v>
       </c>
       <c r="H46" s="17">
-        <v>0.006155227738</v>
+        <v>0.0067819454963</v>
       </c>
       <c r="I46" s="16">
-        <v>9.36</v>
+        <v>7.85</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -2537,28 +2599,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D47" s="14">
-        <v>9.54</v>
+        <v>7.3108</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F47" s="15">
-        <v>420</v>
+        <v>5000</v>
       </c>
       <c r="G47" s="16">
-        <v>4403.71</v>
+        <v>5027.50</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0061176773952</v>
+        <v>0.0067678108342</v>
       </c>
       <c r="I47" s="16">
-        <v>9.3</v>
+        <v>7.02</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2566,28 +2628,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D48" s="14">
-        <v>9.54</v>
+        <v>8.90</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F48" s="15">
-        <v>420</v>
+        <v>5000</v>
       </c>
       <c r="G48" s="16">
-        <v>4385.87</v>
+        <v>5024.4</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0060928938911</v>
+        <v>0.0067636377435</v>
       </c>
       <c r="I48" s="16">
-        <v>9.24</v>
+        <v>7.58</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2595,28 +2657,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>86</v>
       </c>
       <c r="D49" s="14">
-        <v>9.54</v>
+        <v>8.8</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F49" s="15">
-        <v>420</v>
+        <v>5000</v>
       </c>
       <c r="G49" s="16">
-        <v>4366.39</v>
+        <v>5008.01</v>
       </c>
       <c r="H49" s="17">
-        <v>0.0060658320828</v>
+        <v>0.006741574209</v>
       </c>
       <c r="I49" s="16">
-        <v>9.18</v>
+        <v>7.85</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2624,28 +2686,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D50" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F50" s="15">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G50" s="16">
-        <v>4345.15</v>
+        <v>4608.26</v>
       </c>
       <c r="H50" s="17">
-        <v>0.0060363252652</v>
+        <v>0.0062034474301</v>
       </c>
       <c r="I50" s="16">
-        <v>9.12</v>
+        <v>8.93</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2653,28 +2715,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D51" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F51" s="15">
         <v>420</v>
       </c>
       <c r="G51" s="16">
-        <v>4322.02</v>
+        <v>4470.97</v>
       </c>
       <c r="H51" s="17">
-        <v>0.0060041928409</v>
+        <v>0.0060186333576</v>
       </c>
       <c r="I51" s="16">
-        <v>9.04</v>
+        <v>8.95</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -2682,28 +2744,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D52" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F52" s="15">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="G52" s="16">
-        <v>4261.45</v>
+        <v>4442.25</v>
       </c>
       <c r="H52" s="17">
-        <v>0.0059200483991</v>
+        <v>0.0059799716913</v>
       </c>
       <c r="I52" s="16">
-        <v>9.45</v>
+        <v>8.63</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>13</v>
@@ -2711,28 +2773,28 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D53" s="14">
-        <v>8.32</v>
+        <v>9.58</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F53" s="15">
-        <v>4100</v>
+        <v>420</v>
       </c>
       <c r="G53" s="16">
-        <v>4122.99</v>
+        <v>4435.98</v>
       </c>
       <c r="H53" s="17">
-        <v>0.0057276984006</v>
+        <v>0.0059715312788</v>
       </c>
       <c r="I53" s="16">
-        <v>8.03</v>
+        <v>8.81</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>13</v>
@@ -2740,28 +2802,28 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>93</v>
-      </c>
       <c r="D54" s="14">
-        <v>7.9613000000000005</v>
+        <v>9.58</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F54" s="15">
-        <v>4000</v>
+        <v>420</v>
       </c>
       <c r="G54" s="16">
-        <v>4009.25</v>
+        <v>4419.50</v>
       </c>
       <c r="H54" s="17">
-        <v>0.00556968967</v>
+        <v>0.0059493465901</v>
       </c>
       <c r="I54" s="16">
-        <v>7.80</v>
+        <v>8.25</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -2769,28 +2831,28 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D55" s="14">
-        <v>8.45</v>
+        <v>9.58</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="F55" s="15">
-        <v>3500</v>
+        <v>420</v>
       </c>
       <c r="G55" s="16">
-        <v>3506.66</v>
+        <v>4418.47</v>
       </c>
       <c r="H55" s="17">
-        <v>0.0048714866816</v>
+        <v>0.005947960047</v>
       </c>
       <c r="I55" s="16">
-        <v>8.28</v>
+        <v>7.06</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>13</v>
@@ -2798,28 +2860,28 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>97</v>
-      </c>
       <c r="D56" s="14">
-        <v>8.45</v>
+        <v>9.58</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="F56" s="15">
-        <v>3500</v>
+        <v>420</v>
       </c>
       <c r="G56" s="16">
-        <v>3505.01</v>
+        <v>4418.12</v>
       </c>
       <c r="H56" s="17">
-        <v>0.0048691944853</v>
+        <v>0.0059474888916</v>
       </c>
       <c r="I56" s="16">
-        <v>8.32</v>
+        <v>7.64</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>13</v>
@@ -2827,28 +2889,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D57" s="14">
-        <v>8.45</v>
+        <v>9.58</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="F57" s="15">
-        <v>3500</v>
+        <v>420</v>
       </c>
       <c r="G57" s="16">
-        <v>3499.06</v>
+        <v>4417.65</v>
       </c>
       <c r="H57" s="17">
-        <v>0.0048609286866</v>
+        <v>0.0059468561972</v>
       </c>
       <c r="I57" s="16">
-        <v>8.38</v>
+        <v>8.47</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>13</v>
@@ -2856,28 +2918,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D58" s="14">
-        <v>8.45</v>
+        <v>9.58</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="F58" s="15">
-        <v>3500</v>
+        <v>420</v>
       </c>
       <c r="G58" s="16">
-        <v>3495.38</v>
+        <v>4412.92</v>
       </c>
       <c r="H58" s="17">
-        <v>0.0048558163942</v>
+        <v>0.0059404888685</v>
       </c>
       <c r="I58" s="16">
-        <v>8.43</v>
+        <v>8.01</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
@@ -2885,28 +2947,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D59" s="14">
-        <v>6.75</v>
+        <v>9.58</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="F59" s="15">
-        <v>350</v>
+        <v>405</v>
       </c>
       <c r="G59" s="16">
-        <v>3447.83</v>
+        <v>4281.89</v>
       </c>
       <c r="H59" s="17">
-        <v>0.0047897594649</v>
+        <v>0.0057641017469</v>
       </c>
       <c r="I59" s="16">
-        <v>8.66</v>
+        <v>8.83</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -2914,28 +2976,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D60" s="14">
-        <v>8.32</v>
+        <v>7.22</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F60" s="15">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="G60" s="16">
-        <v>2906.29</v>
+        <v>3714.46</v>
       </c>
       <c r="H60" s="17">
-        <v>0.0040374467521</v>
+        <v>0.0050002511449</v>
       </c>
       <c r="I60" s="16">
-        <v>8.10</v>
+        <v>7.26</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -2943,28 +3005,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D61" s="14">
-        <v>7.99</v>
+        <v>8.45</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="F61" s="15">
-        <v>2900</v>
+        <v>3500</v>
       </c>
       <c r="G61" s="16">
-        <v>2905.12</v>
+        <v>3545.80</v>
       </c>
       <c r="H61" s="17">
-        <v>0.0040358213766</v>
+        <v>0.0047732080867</v>
       </c>
       <c r="I61" s="16">
-        <v>8.02</v>
+        <v>7.34</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -2972,28 +3034,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D62" s="14">
-        <v>8.73</v>
+        <v>8.45</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F62" s="15">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G62" s="16">
-        <v>2509.76</v>
+        <v>3529.62</v>
       </c>
       <c r="H62" s="17">
-        <v>0.0034865833625</v>
+        <v>0.0047514272454</v>
       </c>
       <c r="I62" s="16">
-        <v>8.50</v>
+        <v>7.39</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>13</v>
@@ -3001,28 +3063,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D63" s="14">
-        <v>8.73</v>
+        <v>8.45</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F63" s="15">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G63" s="16">
-        <v>2508.12</v>
+        <v>3508.87</v>
       </c>
       <c r="H63" s="17">
-        <v>0.0034843050583</v>
+        <v>0.0047234944608</v>
       </c>
       <c r="I63" s="16">
-        <v>8.53</v>
+        <v>7.30</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>13</v>
@@ -3030,28 +3092,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D64" s="14">
-        <v>7.83</v>
+        <v>6.75</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="F64" s="15">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G64" s="16">
-        <v>2501.16</v>
+        <v>3484.91</v>
       </c>
       <c r="H64" s="17">
-        <v>0.0034746361576</v>
+        <v>0.004691240508</v>
       </c>
       <c r="I64" s="16">
-        <v>7.76</v>
+        <v>7.46</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>13</v>
@@ -3059,28 +3121,28 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D65" s="14">
-        <v>6.50</v>
+        <v>8.32</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F65" s="15">
-        <v>200</v>
+        <v>3100</v>
       </c>
       <c r="G65" s="16">
-        <v>1966.33</v>
+        <v>3161.30</v>
       </c>
       <c r="H65" s="17">
-        <v>0.002731645043</v>
+        <v>0.0042556102218</v>
       </c>
       <c r="I65" s="16">
-        <v>7.80</v>
+        <v>7.07</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>13</v>
@@ -3088,28 +3150,28 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D66" s="14">
-        <v>8.32</v>
+        <v>7.99</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F66" s="15">
-        <v>300</v>
+        <v>2900</v>
       </c>
       <c r="G66" s="16">
-        <v>302.34</v>
+        <v>2937.84</v>
       </c>
       <c r="H66" s="17">
-        <v>0.000420013712</v>
+        <v>0.0039547976889</v>
       </c>
       <c r="I66" s="16">
-        <v>8.02</v>
+        <v>7.09</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>13</v>
@@ -3117,28 +3179,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D67" s="14">
-        <v>8.25</v>
+        <v>8.32</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F67" s="15">
-        <v>10</v>
+        <v>2900</v>
       </c>
       <c r="G67" s="16">
-        <v>100.16</v>
+        <v>2923.60</v>
       </c>
       <c r="H67" s="17">
-        <v>0.0001391432605</v>
+        <v>0.0039356283948</v>
       </c>
       <c r="I67" s="16">
-        <v>7.84</v>
+        <v>7.04</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>13</v>
@@ -3146,36 +3208,57 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>13</v>
+        <v>56</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" s="14">
+        <v>7.48</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G68" s="16">
+        <v>2563.94</v>
+      </c>
+      <c r="H68" s="17">
+        <v>0.003451469102</v>
+      </c>
+      <c r="I68" s="16">
+        <v>6.60</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="I69" s="9" t="s">
-        <v>13</v>
+      <c r="D69" s="14">
+        <v>7.79</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G69" s="16">
+        <v>2552.34</v>
+      </c>
+      <c r="H69" s="17">
+        <v>0.0034358536657</v>
+      </c>
+      <c r="I69" s="16">
+        <v>6.57</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>13</v>
@@ -3183,36 +3266,57 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>13</v>
+        <v>114</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D70" s="14">
+        <v>8.73</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F70" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G70" s="16">
+        <v>2550.46</v>
+      </c>
+      <c r="H70" s="17">
+        <v>0.0034333228881</v>
+      </c>
+      <c r="I70" s="16">
+        <v>7.61</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
-      <c r="B71" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>13</v>
+      <c r="B71" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D71" s="14">
+        <v>7.80</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F71" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G71" s="16">
+        <v>2549.13</v>
+      </c>
+      <c r="H71" s="17">
+        <v>0.0034315324976</v>
+      </c>
+      <c r="I71" s="16">
+        <v>6.57</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
@@ -3220,36 +3324,57 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>13</v>
+        <v>114</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D72" s="14">
+        <v>8.73</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F72" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G72" s="16">
+        <v>2540.95</v>
+      </c>
+      <c r="H72" s="17">
+        <v>0.0034205209227</v>
+      </c>
+      <c r="I72" s="16">
+        <v>7.60</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="9">
-        <v>33661.8</v>
-      </c>
-      <c r="H73" s="10">
-        <v>0.046763304791</v>
-      </c>
-      <c r="I73" s="9" t="s">
-        <v>13</v>
+      <c r="B73" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D73" s="14">
+        <v>7.43</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G73" s="16">
+        <v>2522.74</v>
+      </c>
+      <c r="H73" s="17">
+        <v>0.0033960073801</v>
+      </c>
+      <c r="I73" s="16">
+        <v>6.61</v>
       </c>
       <c r="J73" s="11" t="s">
         <v>13</v>
@@ -3257,28 +3382,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>13</v>
+        <v>119</v>
+      </c>
+      <c r="D74" s="14">
+        <v>7.21</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="F74" s="15">
-        <v>1000000000</v>
+        <v>2500</v>
       </c>
       <c r="G74" s="16">
-        <v>10020</v>
+        <v>2508.26</v>
       </c>
       <c r="H74" s="17">
-        <v>0.0139198828942</v>
+        <v>0.003376515008</v>
       </c>
       <c r="I74" s="16">
-        <v>9.21</v>
+        <v>7.27</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>13</v>
@@ -3286,28 +3411,28 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C75" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>13</v>
+      <c r="D75" s="14">
+        <v>6.07</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="F75" s="15">
-        <v>1000000000</v>
+        <v>250</v>
       </c>
       <c r="G75" s="16">
-        <v>9365</v>
+        <v>2469.77</v>
       </c>
       <c r="H75" s="17">
-        <v>0.0130099504295</v>
+        <v>0.0033247013752</v>
       </c>
       <c r="I75" s="16">
-        <v>9.21</v>
+        <v>6.60</v>
       </c>
       <c r="J75" s="11" t="s">
         <v>13</v>
@@ -3315,28 +3440,28 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C76" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C76" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>13</v>
+      <c r="D76" s="14">
+        <v>6.50</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="F76" s="15">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="G76" s="16">
-        <v>4970.47</v>
+        <v>1991.69</v>
       </c>
       <c r="H76" s="17">
-        <v>0.0069050259809</v>
+        <v>0.0026811300169</v>
       </c>
       <c r="I76" s="16">
-        <v>8.35</v>
+        <v>6.92</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>13</v>
@@ -3344,28 +3469,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C77" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D77" s="13" t="s">
-        <v>13</v>
+      <c r="D77" s="14">
+        <v>8.10</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="F77" s="15">
-        <v>47</v>
+        <v>500</v>
       </c>
       <c r="G77" s="16">
-        <v>4685.83</v>
+        <v>511.54</v>
       </c>
       <c r="H77" s="17">
-        <v>0.0065096012836</v>
+        <v>0.0006886138148</v>
       </c>
       <c r="I77" s="16">
-        <v>8.41</v>
+        <v>6.87</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>13</v>
@@ -3373,28 +3498,28 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C78" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="D78" s="13" t="s">
-        <v>13</v>
+      <c r="D78" s="14">
+        <v>7.9613000000000005</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="F78" s="15">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="G78" s="16">
-        <v>4620.50</v>
+        <v>504.82</v>
       </c>
       <c r="H78" s="17">
-        <v>0.0064188442028</v>
+        <v>0.000679567631</v>
       </c>
       <c r="I78" s="16">
-        <v>8.41</v>
+        <v>6.85</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>13</v>
@@ -3402,36 +3527,57 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>13</v>
+        <v>108</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D79" s="14">
+        <v>8.32</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F79" s="15">
+        <v>300</v>
+      </c>
+      <c r="G79" s="16">
+        <v>308.03</v>
+      </c>
+      <c r="H79" s="17">
+        <v>0.0004146571399</v>
+      </c>
+      <c r="I79" s="16">
+        <v>7.19</v>
       </c>
       <c r="J79" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>13</v>
+      <c r="B80" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D80" s="14">
+        <v>8.25</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" s="15">
+        <v>10</v>
+      </c>
+      <c r="G80" s="16">
+        <v>100.45</v>
+      </c>
+      <c r="H80" s="17">
+        <v>0.0001352216008</v>
+      </c>
+      <c r="I80" s="16">
+        <v>6.74</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>13</v>
@@ -3447,7 +3593,7 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>13</v>
@@ -3462,10 +3608,10 @@
         <v>13</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="I82" s="9" t="s">
         <v>13</v>
@@ -3484,7 +3630,7 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>13</v>
@@ -3499,10 +3645,10 @@
         <v>13</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="I84" s="9" t="s">
         <v>13</v>
@@ -3521,7 +3667,7 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>13</v>
@@ -3535,11 +3681,11 @@
       <c r="F86" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G86" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>114</v>
+      <c r="G86" s="9">
+        <v>28981.980000000003</v>
+      </c>
+      <c r="H86" s="10">
+        <v>0.0390143328176</v>
       </c>
       <c r="I86" s="9" t="s">
         <v>13</v>
@@ -3550,36 +3696,57 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>13</v>
+        <v>132</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F87" s="15">
+        <v>1000000000</v>
+      </c>
+      <c r="G87" s="16">
+        <v>9031</v>
+      </c>
+      <c r="H87" s="17">
+        <v>0.0121571555731</v>
+      </c>
+      <c r="I87" s="16">
+        <v>8.60</v>
       </c>
       <c r="J87" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="I88" s="9" t="s">
-        <v>13</v>
+      <c r="B88" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F88" s="15">
+        <v>1000000000</v>
+      </c>
+      <c r="G88" s="16">
+        <v>7088</v>
+      </c>
+      <c r="H88" s="17">
+        <v>0.0095415700035</v>
+      </c>
+      <c r="I88" s="16">
+        <v>8.58</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>13</v>
@@ -3587,36 +3754,57 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>13</v>
+        <v>137</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F89" s="15">
+        <v>47</v>
+      </c>
+      <c r="G89" s="16">
+        <v>4683.08</v>
+      </c>
+      <c r="H89" s="17">
+        <v>0.0063041669938</v>
+      </c>
+      <c r="I89" s="16">
+        <v>7.76</v>
       </c>
       <c r="J89" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H90" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="I90" s="9" t="s">
-        <v>13</v>
+      <c r="B90" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F90" s="15">
+        <v>48</v>
+      </c>
+      <c r="G90" s="16">
+        <v>4282.64</v>
+      </c>
+      <c r="H90" s="17">
+        <v>0.0057651113657</v>
+      </c>
+      <c r="I90" s="16">
+        <v>7.58</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>13</v>
@@ -3624,35 +3812,35 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="12" t="s">
-        <v>13</v>
+        <v>137</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F91" s="15">
+        <v>55</v>
+      </c>
+      <c r="G91" s="16">
+        <v>3897.26</v>
+      </c>
+      <c r="H91" s="17">
+        <v>0.0052463288815</v>
+      </c>
+      <c r="I91" s="16">
+        <v>7.39</v>
       </c>
       <c r="J91" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H92" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="I92" s="9" t="s">
+      <c r="B92" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J92" s="11" t="s">
@@ -3660,7 +3848,28 @@
       </c>
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I93" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J93" s="11" t="s">
@@ -3668,28 +3877,7 @@
       </c>
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
-      <c r="B94" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="I94" s="9" t="s">
+      <c r="B94" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J94" s="11" t="s">
@@ -3697,7 +3885,28 @@
       </c>
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I95" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J95" s="11" t="s">
@@ -3705,28 +3914,7 @@
       </c>
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
-      <c r="B96" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F96" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" s="9">
-        <v>3236.44</v>
-      </c>
-      <c r="H96" s="10">
-        <v>0.0044960943906</v>
-      </c>
-      <c r="I96" s="9" t="s">
+      <c r="B96" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J96" s="11" t="s">
@@ -3734,28 +3922,28 @@
       </c>
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="C97" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F97" s="15">
-        <v>29663.317</v>
-      </c>
-      <c r="G97" s="16">
-        <v>3236.44</v>
-      </c>
-      <c r="H97" s="17">
-        <v>0.0044960943906</v>
-      </c>
-      <c r="I97" s="16" t="s">
+      <c r="B97" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I97" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J97" s="11" t="s">
@@ -3772,7 +3960,7 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="7" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>13</v>
@@ -3786,11 +3974,11 @@
       <c r="F99" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G99" s="9">
-        <v>5172.19</v>
-      </c>
-      <c r="H99" s="10">
-        <v>0.0071852573958</v>
+      <c r="G99" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="I99" s="9" t="s">
         <v>13</v>
@@ -3808,144 +3996,102 @@
       </c>
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
-      <c r="B101" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D101" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F101" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="19">
-        <v>14226.23200190009</v>
-      </c>
-      <c r="H101" s="20">
-        <v>0.019763221905461512</v>
-      </c>
-      <c r="I101" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J101" s="21" t="s">
+      <c r="B101" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J101" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
-      <c r="B102" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D102" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G102" s="19">
-        <v>719833.6420019</v>
-      </c>
-      <c r="H102" s="20">
-        <v>0.9999999999968614</v>
-      </c>
-      <c r="I102" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J102" s="21" t="s">
+      <c r="B102" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
-      <c r="B103" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D103" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F103" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H103" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="I103" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J103" s="21" t="s">
+      <c r="B103" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J103" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D104" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="19">
-        <v>-135000</v>
-      </c>
-      <c r="H104" s="20">
-        <v>-0.1875433324074115</v>
-      </c>
-      <c r="I104" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J104" s="21" t="s">
+      <c r="B104" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J104" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
-      <c r="B105" s="12" t="s">
-        <v>142</v>
+      <c r="B105" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="D105" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H105" s="17">
-        <v>-0.013892098696845297</v>
-      </c>
-      <c r="I105" s="8" t="s">
+      <c r="F105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I105" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J105" s="11" t="s">
@@ -3954,27 +4100,6 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
       <c r="B106" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G106" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H106" s="17">
-        <v>-0.013892098696845297</v>
-      </c>
-      <c r="I106" s="8" t="s">
         <v>13</v>
       </c>
       <c r="J106" s="11" t="s">
@@ -3982,28 +4107,28 @@
       </c>
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
-      <c r="B107" s="12" t="s">
-        <v>144</v>
+      <c r="B107" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D107" s="8" t="s">
+      <c r="D107" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E107" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F107" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G107" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H107" s="17">
-        <v>-0.013892098696845297</v>
-      </c>
-      <c r="I107" s="8" t="s">
+      <c r="F107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I107" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J107" s="11" t="s">
@@ -4012,27 +4137,6 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
       <c r="B108" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H108" s="17">
-        <v>-0.013892098696845297</v>
-      </c>
-      <c r="I108" s="8" t="s">
         <v>13</v>
       </c>
       <c r="J108" s="11" t="s">
@@ -4040,28 +4144,28 @@
       </c>
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
-      <c r="B109" s="12" t="s">
-        <v>146</v>
+      <c r="B109" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D109" s="8" t="s">
+      <c r="D109" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F109" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H109" s="17">
-        <v>-0.013892098696845297</v>
-      </c>
-      <c r="I109" s="8" t="s">
+      <c r="F109" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="9">
+        <v>3319.61</v>
+      </c>
+      <c r="H109" s="10">
+        <v>0.0044687205417</v>
+      </c>
+      <c r="I109" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J109" s="11" t="s">
@@ -4070,27 +4174,27 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>13</v>
+        <v>150</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F110" s="15">
+        <v>29663.317</v>
       </c>
       <c r="G110" s="16">
-        <v>-10000</v>
+        <v>3319.61</v>
       </c>
       <c r="H110" s="17">
-        <v>-0.013892098696845297</v>
-      </c>
-      <c r="I110" s="8" t="s">
+        <v>0.0044687205417</v>
+      </c>
+      <c r="I110" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J110" s="11" t="s">
@@ -4099,27 +4203,6 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D111" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G111" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H111" s="17">
-        <v>-0.013892098696845297</v>
-      </c>
-      <c r="I111" s="8" t="s">
         <v>13</v>
       </c>
       <c r="J111" s="11" t="s">
@@ -4127,28 +4210,28 @@
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="12" t="s">
-        <v>148</v>
+      <c r="B112" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D112" s="8" t="s">
+      <c r="D112" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="16">
-        <v>-5000</v>
-      </c>
-      <c r="H112" s="17">
-        <v>-0.0069460493484226485</v>
-      </c>
-      <c r="I112" s="8" t="s">
+      <c r="F112" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="9">
+        <v>6698.85</v>
+      </c>
+      <c r="H112" s="10">
+        <v>0.0090177125026</v>
+      </c>
+      <c r="I112" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J112" s="11" t="s">
@@ -4157,27 +4240,6 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
       <c r="B113" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" s="16">
-        <v>-5000</v>
-      </c>
-      <c r="H113" s="17">
-        <v>-0.0069460493484226485</v>
-      </c>
-      <c r="I113" s="8" t="s">
         <v>13</v>
       </c>
       <c r="J113" s="11" t="s">
@@ -4185,124 +4247,124 @@
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
-      <c r="B114" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="16">
-        <v>-5000</v>
-      </c>
-      <c r="H114" s="17">
-        <v>-0.0069460493484226485</v>
-      </c>
-      <c r="I114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J114" s="11" t="s">
+      <c r="B114" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C114" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="20">
+        <v>11389.867157359957</v>
+      </c>
+      <c r="H114" s="21">
+        <v>0.015332564166680992</v>
+      </c>
+      <c r="I114" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J114" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
-      <c r="B115" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G115" s="16">
-        <v>-20000</v>
-      </c>
-      <c r="H115" s="17">
-        <v>-0.027784197393690594</v>
-      </c>
-      <c r="I115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J115" s="11" t="s">
+      <c r="B115" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C115" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="20">
+        <v>742854.68715736</v>
+      </c>
+      <c r="H115" s="21">
+        <v>0.9999999999960809</v>
+      </c>
+      <c r="I115" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J115" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H116" s="17">
-        <v>-0.013892098696845297</v>
-      </c>
-      <c r="I116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J116" s="11" t="s">
+      <c r="B116" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H116" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J116" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
-      <c r="B117" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D117" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F117" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="16">
-        <v>-10000</v>
-      </c>
-      <c r="H117" s="17">
-        <v>-0.013892098696845297</v>
-      </c>
-      <c r="I117" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J117" s="11" t="s">
+      <c r="B117" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C117" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="20">
+        <v>-157500</v>
+      </c>
+      <c r="H117" s="21">
+        <v>-0.21201993165405783</v>
+      </c>
+      <c r="I117" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J117" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
       <c r="B118" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>13</v>
@@ -4320,7 +4382,7 @@
         <v>-10000</v>
       </c>
       <c r="H118" s="17">
-        <v>-0.013892098696845297</v>
+        <v>-0.013461582962162402</v>
       </c>
       <c r="I118" s="8" t="s">
         <v>13</v>
@@ -4330,150 +4392,626 @@
       </c>
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
-      <c r="B119" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C119" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D119" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F119" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G119" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H119" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="I119" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="J119" s="22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="122" spans="2:9" ht="15" customHeight="1">
-      <c r="B122" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C122" s="23"/>
-      <c r="D122" s="23"/>
-      <c r="E122" s="23"/>
-      <c r="F122" s="23"/>
-      <c r="G122" s="23"/>
-      <c r="H122" s="23"/>
-      <c r="I122" s="23"/>
-    </row>
-    <row r="123" spans="2:8" ht="15" customHeight="1">
-      <c r="B123" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="C123" s="23"/>
-      <c r="D123" s="23"/>
-      <c r="E123" s="23"/>
-      <c r="F123" s="23"/>
-      <c r="G123" s="23"/>
-      <c r="H123" s="23"/>
-    </row>
-    <row r="124" spans="2:8" ht="15" customHeight="1">
-      <c r="B124" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C124" s="23"/>
-      <c r="D124" s="23"/>
-      <c r="E124" s="23"/>
-      <c r="F124" s="23"/>
-      <c r="G124" s="23"/>
-      <c r="H124" s="23"/>
-    </row>
-    <row r="125" spans="2:8" ht="15" customHeight="1">
-      <c r="B125" s="13" t="s">
+      <c r="B119" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="C125" s="23"/>
-      <c r="D125" s="23"/>
-      <c r="E125" s="23"/>
-      <c r="F125" s="23"/>
-      <c r="G125" s="23"/>
-      <c r="H125" s="23"/>
-    </row>
-    <row r="126" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B126" s="24" t="s">
+      <c r="C119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" s="16">
+        <v>-20000</v>
+      </c>
+      <c r="H119" s="17">
+        <v>-0.026923165924324803</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J119" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="2:10" ht="15" customHeight="1">
+      <c r="B120" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="C126" s="23"/>
-      <c r="D126" s="23"/>
-      <c r="E126" s="23"/>
-      <c r="F126" s="23"/>
-      <c r="G126" s="23"/>
-      <c r="H126" s="23"/>
-    </row>
-    <row r="127" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B127" s="24" t="s">
+      <c r="C120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H120" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10" ht="15" customHeight="1">
+      <c r="B121" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C127" s="23"/>
-      <c r="D127" s="23"/>
-      <c r="E127" s="23"/>
-      <c r="F127" s="23"/>
-      <c r="G127" s="23"/>
-      <c r="H127" s="23"/>
-    </row>
-    <row r="128" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B128" s="24" t="s">
+      <c r="C121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H121" s="17">
+        <v>-0.006730791481081201</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J121" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10" ht="15" customHeight="1">
+      <c r="B122" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="C128" s="23"/>
-      <c r="D128" s="23"/>
-      <c r="E128" s="23"/>
-      <c r="F128" s="23"/>
-      <c r="G128" s="23"/>
-      <c r="H128" s="23"/>
-    </row>
-    <row r="129" spans="2:7" ht="54" customHeight="1">
-      <c r="B129" s="25" t="s">
+      <c r="C122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H122" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J122" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10" ht="15" customHeight="1">
+      <c r="B123" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C129" s="25"/>
-      <c r="D129" s="25"/>
-      <c r="E129" s="25"/>
-      <c r="F129" s="25"/>
-      <c r="G129" s="25"/>
-    </row>
-    <row r="132" ht="15">
-      <c r="B132" s="23" t="s">
+      <c r="C123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H123" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J123" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10" ht="15" customHeight="1">
+      <c r="B124" s="12" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="147" ht="15">
-      <c r="B147" s="23" t="s">
+      <c r="C124" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H124" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J124" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" ht="15" customHeight="1">
+      <c r="B125" s="12" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="148" ht="15">
-      <c r="B148" s="23" t="s">
+      <c r="C125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H125" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J125" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10" ht="15" customHeight="1">
+      <c r="B126" s="12" t="s">
         <v>165</v>
       </c>
+      <c r="C126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H126" s="17">
+        <v>-0.010096187221621802</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J126" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" ht="15" customHeight="1">
+      <c r="B127" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H127" s="17">
+        <v>-0.006730791481081201</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J127" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" ht="15" customHeight="1">
+      <c r="B128" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H128" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J128" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" ht="15" customHeight="1">
+      <c r="B129" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H129" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" ht="15" customHeight="1">
+      <c r="B130" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H130" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" ht="15" customHeight="1">
+      <c r="B131" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H131" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J131" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10" ht="15" customHeight="1">
+      <c r="B132" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H132" s="17">
+        <v>-0.006730791481081201</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J132" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" ht="15" customHeight="1">
+      <c r="B133" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H133" s="17">
+        <v>-0.006730791481081201</v>
+      </c>
+      <c r="I133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J133" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" ht="15" customHeight="1">
+      <c r="B134" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H134" s="17">
+        <v>-0.013461582962162402</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J134" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="2:10" ht="15" customHeight="1">
+      <c r="B135" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C135" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D135" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I135" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J135" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9" ht="15" customHeight="1">
+      <c r="B138" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="C138" s="24"/>
+      <c r="D138" s="24"/>
+      <c r="E138" s="24"/>
+      <c r="F138" s="24"/>
+      <c r="G138" s="24"/>
+      <c r="H138" s="24"/>
+      <c r="I138" s="24"/>
+    </row>
+    <row r="139" spans="2:8" ht="15" customHeight="1">
+      <c r="B139" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C139" s="24"/>
+      <c r="D139" s="24"/>
+      <c r="E139" s="24"/>
+      <c r="F139" s="24"/>
+      <c r="G139" s="24"/>
+      <c r="H139" s="24"/>
+    </row>
+    <row r="140" spans="2:8" ht="15" customHeight="1">
+      <c r="B140" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C140" s="24"/>
+      <c r="D140" s="24"/>
+      <c r="E140" s="24"/>
+      <c r="F140" s="24"/>
+      <c r="G140" s="24"/>
+      <c r="H140" s="24"/>
+    </row>
+    <row r="141" spans="2:8" ht="15" customHeight="1">
+      <c r="B141" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C141" s="24"/>
+      <c r="D141" s="24"/>
+      <c r="E141" s="24"/>
+      <c r="F141" s="24"/>
+      <c r="G141" s="24"/>
+      <c r="H141" s="24"/>
+    </row>
+    <row r="142" spans="2:8" ht="15" customHeight="1">
+      <c r="B142" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C142" s="24"/>
+      <c r="D142" s="24"/>
+      <c r="E142" s="24"/>
+      <c r="F142" s="24"/>
+      <c r="G142" s="24"/>
+      <c r="H142" s="24"/>
+    </row>
+    <row r="143" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B143" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="C143" s="24"/>
+      <c r="D143" s="24"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+    </row>
+    <row r="144" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B144" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="C144" s="24"/>
+      <c r="D144" s="24"/>
+      <c r="E144" s="24"/>
+      <c r="F144" s="24"/>
+      <c r="G144" s="24"/>
+      <c r="H144" s="24"/>
+    </row>
+    <row r="145" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B145" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="C145" s="24"/>
+      <c r="D145" s="24"/>
+      <c r="E145" s="24"/>
+      <c r="F145" s="24"/>
+      <c r="G145" s="24"/>
+      <c r="H145" s="24"/>
+    </row>
+    <row r="146" spans="2:7" ht="46.5" customHeight="1">
+      <c r="B146" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="C146" s="26"/>
+      <c r="D146" s="26"/>
+      <c r="E146" s="26"/>
+      <c r="F146" s="26"/>
+      <c r="G146" s="26"/>
+    </row>
+    <row r="149" ht="15">
+      <c r="B149" s="24" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="164" ht="15">
+      <c r="B164" s="24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="165" ht="15">
+      <c r="B165" s="24" t="s">
+        <v>184</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B129:G129"/>
-    <mergeCell ref="B124:H124"/>
-    <mergeCell ref="B125:H125"/>
-    <mergeCell ref="B126:H126"/>
-    <mergeCell ref="B127:H127"/>
-    <mergeCell ref="B128:H128"/>
+  <mergeCells count="12">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B122:I122"/>
-    <mergeCell ref="B123:H123"/>
+    <mergeCell ref="B138:I138"/>
+    <mergeCell ref="B139:H139"/>
+    <mergeCell ref="B145:H145"/>
+    <mergeCell ref="B146:G146"/>
+    <mergeCell ref="B140:H140"/>
+    <mergeCell ref="B141:H141"/>
+    <mergeCell ref="B142:H142"/>
+    <mergeCell ref="B143:H143"/>
+    <mergeCell ref="B144:H144"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
